--- a/Data/All Ratios.xlsx
+++ b/Data/All Ratios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jonat\Documents\Calpoly MSBA\Spring\Finance Analytics\Project 2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C25A04-169C-4276-9ABC-581E0E05277C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA94C239-998D-4A26-92A3-99B7BD609A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="3" xr2:uid="{3F429AB5-DD66-46F0-A60F-19AD966D66FF}"/>
+    <workbookView xWindow="4540" yWindow="2130" windowWidth="15330" windowHeight="10770" firstSheet="1" activeTab="3" xr2:uid="{3F429AB5-DD66-46F0-A60F-19AD966D66FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Income Statement" sheetId="2" r:id="rId1"/>
@@ -1252,7 +1252,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1309,9 +1309,8 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
@@ -23855,10 +23854,7 @@
         <f t="shared" si="11"/>
         <v>-1813</v>
       </c>
-      <c r="AH20" s="3">
-        <f t="shared" si="12"/>
-        <v>1.0852130325814537</v>
-      </c>
+      <c r="AH20" s="3"/>
       <c r="AI20" s="3">
         <f t="shared" si="13"/>
         <v>0.52043269230769229</v>
@@ -23968,7 +23964,7 @@
         <f>-'Cash Flow'!F21</f>
         <v>216</v>
       </c>
-      <c r="U21" s="49"/>
+      <c r="U21" s="48"/>
       <c r="V21" s="10">
         <f t="shared" si="1"/>
         <v>0.22929698440855195</v>
@@ -24005,11 +24001,11 @@
         <f t="shared" si="9"/>
         <v>4.3548017419206969E-2</v>
       </c>
-      <c r="AE21" s="50">
+      <c r="AE21" s="49">
         <f>(I21+'Balance Sheet'!E21)/L21</f>
         <v>0.94826224328594</v>
       </c>
-      <c r="AF21" s="50">
+      <c r="AF21" s="49">
         <f t="shared" si="10"/>
         <v>1.3321484992101107</v>
       </c>
@@ -24017,23 +24013,20 @@
         <f t="shared" si="11"/>
         <v>-756</v>
       </c>
-      <c r="AH21" s="50">
-        <f t="shared" si="12"/>
-        <v>2.9303944315545243</v>
-      </c>
-      <c r="AI21" s="50">
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="49">
         <f t="shared" si="13"/>
         <v>0.74557260920897284</v>
       </c>
-      <c r="AJ21" s="50">
+      <c r="AJ21" s="49">
         <f t="shared" si="14"/>
         <v>0.28947971579188631</v>
       </c>
-      <c r="AK21" s="50">
+      <c r="AK21" s="49">
         <f t="shared" si="15"/>
         <v>4.9871794871794872</v>
       </c>
-      <c r="AL21" s="50">
+      <c r="AL21" s="49">
         <f t="shared" si="16"/>
         <v>10.122969837587007</v>
       </c>
@@ -27271,11 +27264,11 @@
         <f t="shared" si="28"/>
         <v>0.18102791787002312</v>
       </c>
-      <c r="AE41" s="50">
+      <c r="AE41" s="49">
         <f>(I41+'Balance Sheet'!E41)/L41</f>
         <v>1.9373050530255771</v>
       </c>
-      <c r="AF41" s="50">
+      <c r="AF41" s="49">
         <f t="shared" si="29"/>
         <v>2.1838517066215131</v>
       </c>
@@ -27283,20 +27276,20 @@
         <f t="shared" si="30"/>
         <v>-34161</v>
       </c>
-      <c r="AH41" s="50">
+      <c r="AH41" s="49">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AI41" s="50">
+      <c r="AI41" s="49">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="AJ41" s="50">
+      <c r="AJ41" s="49">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AK41" s="50"/>
-      <c r="AL41" s="50">
+      <c r="AK41" s="49"/>
+      <c r="AL41" s="49">
         <f t="shared" si="35"/>
         <v>1.7354129263913824</v>
       </c>
@@ -30548,11 +30541,11 @@
         <f t="shared" si="28"/>
         <v>0.16658840077255069</v>
       </c>
-      <c r="AE61" s="50">
+      <c r="AE61" s="49">
         <f>(I61+'Balance Sheet'!E61)/L61</f>
         <v>9.6323618125889663</v>
       </c>
-      <c r="AF61" s="50">
+      <c r="AF61" s="49">
         <f t="shared" si="29"/>
         <v>9.9953832132314666</v>
       </c>
@@ -30560,23 +30553,23 @@
         <f t="shared" si="30"/>
         <v>-11243.914000000001</v>
       </c>
-      <c r="AH61" s="50">
+      <c r="AH61" s="49">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="AI61" s="50">
+      <c r="AI61" s="49">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="AJ61" s="50">
+      <c r="AJ61" s="49">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="AK61" s="50">
+      <c r="AK61" s="49">
         <f t="shared" si="34"/>
         <v>13.813214007782102</v>
       </c>
-      <c r="AL61" s="50">
+      <c r="AL61" s="49">
         <f t="shared" si="35"/>
         <v>1.0841270223194583</v>
       </c>
@@ -30674,7 +30667,7 @@
         <v>69691</v>
       </c>
       <c r="U62" s="4">
-        <f t="shared" ref="U62:U78" si="37">(C62-C63)/C63</f>
+        <f t="shared" ref="U62:U76" si="37">(C62-C63)/C63</f>
         <v>0.22167038498246211</v>
       </c>
       <c r="V62" s="5">
@@ -31342,35 +31335,35 @@
         <v>0.80794376277251567</v>
       </c>
       <c r="W66" s="5">
-        <f t="shared" ref="W66:W80" si="39">E66/C66</f>
+        <f t="shared" ref="W66:W78" si="39">E66/C66</f>
         <v>0.46400800481645738</v>
       </c>
       <c r="X66" s="5">
-        <f t="shared" ref="X66:X80" si="40">F66/C66</f>
+        <f t="shared" ref="X66:X78" si="40">F66/C66</f>
         <v>0.39645040660058173</v>
       </c>
       <c r="Y66" s="5">
-        <f t="shared" ref="Y66:Y80" si="41">G66/C66</f>
+        <f t="shared" ref="Y66:Y78" si="41">G66/C66</f>
         <v>0.40095311585784665</v>
       </c>
       <c r="Z66" s="5">
-        <f t="shared" ref="Z66:Z80" si="42">(G66-H66)/G66</f>
+        <f t="shared" ref="Z66:Z78" si="42">(G66-H66)/G66</f>
         <v>0.16737162676592504</v>
       </c>
       <c r="AA66" s="5">
-        <f t="shared" ref="AA66:AA80" si="43">H66/C66</f>
+        <f t="shared" ref="AA66:AA78" si="43">H66/C66</f>
         <v>0.33384494059985248</v>
       </c>
       <c r="AB66" s="5">
-        <f t="shared" ref="AB66:AB80" si="44">H66/M66</f>
+        <f t="shared" ref="AB66:AB78" si="44">H66/M66</f>
         <v>0.31526517669103693</v>
       </c>
       <c r="AC66" s="5">
-        <f t="shared" ref="AC66:AC80" si="45">(F66*(1-Z66))/(Q66-I66+M66)</f>
+        <f t="shared" ref="AC66:AC78" si="45">(F66*(1-Z66))/(Q66-I66+M66)</f>
         <v>0.50633933395523867</v>
       </c>
       <c r="AD66" s="5">
-        <f t="shared" ref="AD66:AD80" si="46">H66/K66</f>
+        <f t="shared" ref="AD66:AD78" si="46">H66/K66</f>
         <v>0.23718724960388465</v>
       </c>
       <c r="AE66" s="3">
@@ -31378,7 +31371,7 @@
         <v>2.9352732434350601</v>
       </c>
       <c r="AF66" s="3">
-        <f t="shared" ref="AF66:AF80" si="47">J66/L66</f>
+        <f t="shared" ref="AF66:AF77" si="47">J66/L66</f>
         <v>3.1542938254080908</v>
       </c>
       <c r="AG66" s="2">
@@ -32370,7 +32363,7 @@
         <v>4.0682494383386973E-3</v>
       </c>
       <c r="AK72" s="3">
-        <f t="shared" ref="AK66:AK80" si="55">F72/N72</f>
+        <f t="shared" ref="AK72:AK80" si="55">F72/N72</f>
         <v>270.6521739130435</v>
       </c>
       <c r="AL72" s="3">
@@ -32612,7 +32605,7 @@
         <f>'Balance Sheet'!AL74</f>
         <v>15470</v>
       </c>
-      <c r="N74" s="46">
+      <c r="N74" s="41">
         <v>56</v>
       </c>
       <c r="O74" s="40">
@@ -32777,7 +32770,7 @@
         <f>'Balance Sheet'!AL75</f>
         <v>11755</v>
       </c>
-      <c r="N75" s="46">
+      <c r="N75" s="41">
         <v>51</v>
       </c>
       <c r="O75" s="40">
@@ -32942,7 +32935,7 @@
         <f>'Balance Sheet'!AL76</f>
         <v>4899</v>
       </c>
-      <c r="N76" s="46">
+      <c r="N76" s="41">
         <v>42</v>
       </c>
       <c r="O76" s="40">
@@ -33107,7 +33100,7 @@
         <f>'Balance Sheet'!AL77</f>
         <v>2162</v>
       </c>
-      <c r="N77" s="46">
+      <c r="N77" s="41">
         <v>22</v>
       </c>
       <c r="O77" s="40">
@@ -33130,10 +33123,7 @@
         <f>-'Cash Flow'!F77</f>
         <v>293</v>
       </c>
-      <c r="U77" s="4">
-        <f t="shared" si="37"/>
-        <v>1.5405405405405406</v>
-      </c>
+      <c r="U77" s="4"/>
       <c r="V77" s="5">
         <f t="shared" si="38"/>
         <v>0.75025329280648434</v>
@@ -33292,10 +33282,7 @@
         <f>-'Cash Flow'!F78</f>
         <v>33</v>
       </c>
-      <c r="U78" s="4">
-        <f t="shared" si="37"/>
-        <v>1.8566176470588236</v>
-      </c>
+      <c r="U78" s="4"/>
       <c r="V78" s="5">
         <f t="shared" si="38"/>
         <v>0.71299871299871298</v>
@@ -33439,48 +33426,21 @@
       <c r="S79" s="40">
         <v>0</v>
       </c>
-      <c r="T79" s="47">
+      <c r="T79" s="46">
         <v>0</v>
-      </c>
-      <c r="U79">
-        <v>-0.20199999999999999</v>
       </c>
       <c r="V79" s="5">
         <f t="shared" si="38"/>
         <v>0.54411764705882348</v>
       </c>
-      <c r="W79" s="5">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X79" s="5">
-        <f t="shared" si="40"/>
-        <v>-0.20220588235294118</v>
-      </c>
-      <c r="Y79" s="5">
-        <f t="shared" si="41"/>
-        <v>-0.20588235294117646</v>
-      </c>
-      <c r="Z79" s="5">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AA79" s="5">
-        <f t="shared" si="43"/>
-        <v>-0.20588235294117646</v>
-      </c>
-      <c r="AB79" s="5">
-        <f t="shared" si="44"/>
-        <v>-0.16716417910447762</v>
-      </c>
-      <c r="AC79" s="5">
-        <f t="shared" si="45"/>
-        <v>-1.4473684210526316</v>
-      </c>
-      <c r="AD79" s="5">
-        <f t="shared" si="46"/>
-        <v>-0.11089108910891089</v>
-      </c>
+      <c r="W79" s="5"/>
+      <c r="X79" s="5"/>
+      <c r="Y79" s="5"/>
+      <c r="Z79" s="5"/>
+      <c r="AA79" s="5"/>
+      <c r="AB79" s="5"/>
+      <c r="AC79" s="5"/>
+      <c r="AD79" s="5"/>
       <c r="AE79" s="3"/>
       <c r="AF79" s="3"/>
       <c r="AG79" s="2">
@@ -33507,10 +33467,7 @@
         <f t="shared" si="52"/>
         <v>1.5074626865671641</v>
       </c>
-      <c r="AO79" s="5">
-        <f>('Cash Flow'!E79+'Cash Flow'!F79)/Ratios!C79</f>
-        <v>-0.22794117647058823</v>
-      </c>
+      <c r="AO79" s="5"/>
     </row>
     <row r="80" spans="1:43" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
@@ -33572,80 +33529,51 @@
       <c r="S80" s="45">
         <v>0</v>
       </c>
-      <c r="T80" s="48">
+      <c r="T80" s="47">
         <v>0</v>
       </c>
-      <c r="U80" s="7">
-        <v>-0.81099999999999994</v>
-      </c>
+      <c r="U80" s="7"/>
       <c r="V80" s="10">
         <f t="shared" si="38"/>
         <v>0.73202614379084963</v>
       </c>
-      <c r="W80" s="10">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X80" s="10">
-        <f t="shared" si="40"/>
-        <v>-0.81045751633986929</v>
-      </c>
-      <c r="Y80" s="10">
-        <f t="shared" si="41"/>
-        <v>-0.90196078431372551</v>
-      </c>
-      <c r="Z80" s="10">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="AA80" s="10">
-        <f t="shared" si="43"/>
-        <v>-0.90196078431372551</v>
-      </c>
-      <c r="AB80" s="10">
-        <f t="shared" si="44"/>
-        <v>-0.50549450549450547</v>
-      </c>
-      <c r="AC80" s="10">
-        <f t="shared" si="45"/>
-        <v>3.875</v>
-      </c>
-      <c r="AD80" s="10">
-        <f t="shared" si="46"/>
-        <v>-0.3080357142857143</v>
-      </c>
-      <c r="AE80" s="50"/>
-      <c r="AF80" s="50"/>
+      <c r="W80" s="10"/>
+      <c r="X80" s="10"/>
+      <c r="Y80" s="10"/>
+      <c r="Z80" s="10"/>
+      <c r="AA80" s="10"/>
+      <c r="AB80" s="10"/>
+      <c r="AC80" s="10"/>
+      <c r="AD80" s="10"/>
+      <c r="AE80" s="49"/>
+      <c r="AF80" s="49"/>
       <c r="AG80" s="9">
         <f t="shared" si="48"/>
         <v>-305</v>
       </c>
-      <c r="AH80" s="50">
+      <c r="AH80" s="49">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
-      <c r="AI80" s="50">
+      <c r="AI80" s="49">
         <f t="shared" si="50"/>
         <v>0</v>
       </c>
-      <c r="AJ80" s="50">
+      <c r="AJ80" s="49">
         <f t="shared" si="51"/>
         <v>0</v>
       </c>
-      <c r="AK80" s="50">
+      <c r="AK80" s="49">
         <f t="shared" si="55"/>
         <v>-11.272727272727273</v>
       </c>
-      <c r="AL80" s="50">
+      <c r="AL80" s="49">
         <f t="shared" si="52"/>
         <v>1.641025641025641</v>
       </c>
       <c r="AM80" s="7"/>
       <c r="AN80" s="7"/>
-      <c r="AO80" s="10">
-        <f>('Cash Flow'!E80+'Cash Flow'!F80)/Ratios!C80</f>
-        <v>-0.28758169934640521</v>
-      </c>
+      <c r="AO80" s="10"/>
       <c r="AP80" s="7"/>
       <c r="AQ80" s="7"/>
     </row>
